--- a/wb_parser/output/wildberries_catalog_filtered.xlsx
+++ b/wb_parser/output/wildberries_catalog_filtered.xlsx
@@ -49,9 +49,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -419,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -504,6 +507,4729 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/218700008/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>218700008</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное оверсайз</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4577</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Если ищете базовый, но в то же время стильный способ сказать весне и осени «привет», это женская верхняя одежда для вас. Дизайнерская коллекция вдохновлена трендами Pinterest, чтобы даже школьная форма выглядела как будто вы только что вернулись с модного показа. Классическая модель с воротником, поясом и рукавом сразу намекает: тут мода не просто приходит — она правит бал! Для девушек, женщин, подростков и девочек — каждый найдет свой образ. Трендовая длина подходит невысоким барышням и тем, кто любит короткое пальто. Подчеркнутая талия делает его отличным вариантом для беременных или просто поклонниц деловой офисной одежды.
+Этот стильный и удобный вариант из Киргизии разработан специально для тех, кто ценит комфорт и элегантность в одном флаконе. Теплая ткань сохраняет уют даже при переменчивой погоде, а универсальный дизайн легко впишется в повседневный образ. В 2025 году такой выбор станет настоящей находкой для модниц, которые предпочитают брендовые вещи с характером и душой. Размеров много, так что подобрать подходящий вариант не составит труда.
+Модная деталь — драповое полотно с натуральным составом: тепло встречает даже капризную погоду. Весенняя свежесть и осенняя строгость сочетаются в каждой строчке этой вещи. Неважно, идете ли вы в школу или на работу, пальто легко впишется в любой офис или даже школу для подростка.
+</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/1.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/2.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/3.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/4.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/5.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/6.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/7.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/8.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/9.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/10.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/11.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/12.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/13.webp, https://basket-14.wbbasket.ru/vol2187/part218700/218700008/images/big/14.webp</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "полиамид; полиэстeр; шерсть",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "черный",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "черный"
+        ],
+        "variable_value_IDs": [
+          13600062
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "Круглогодичный",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "175 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "89-66-96",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утеплителя",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +15 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "свободный",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "двубортная",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "сухая химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто - 1; Пояс - 1; Вешалка - 1; чехол - 1",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>KUMAYIBA</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/757552</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/306851160/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>306851160</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное прямое с поясом</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4042</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Длинное шерстяное двубортное женское пальто макси прямого кроя из плотной драповой ткани из натуральной шерсти идеально подойдет для осени и весны.
+Широкий отложной воротник с лацканами. Длинные свободные рукава с прямыми манжетами. Два прорезных кармана без застежки по бокам. Застежка на крупные пуговицы спереди, пояс в комплекте. Прямой нижний край с длинной шлицей (разрезом) сзади
+Классическое однотонное плотное серое пальто из новой весенней коллекции. Теплое демисезонное пальто классического кроя с натуральной шерстью в составе защитит от холодных весенних и осенних ветров и других капризов погоды. Стильное и универсальное: создавай самые теплые и женственные аутфиты на каждый день.
+Пальто будет прекрасно выглядить как в классических строгих образах, так и стильно будет смотреться в кэжуал повседневных образах.Для беременных девушек - это действительно комфортное решение, а его приталенная форма с поясом подчеркнет вашу фигуру, придавая изящство. Также это оверсайз пальто впишется в молодежный стиль и идеально подойдет на работу, в школу или университет.Если вы ищете теплую верхнюю одежду для женщин, это пальто может стать вашим идеальным выбором.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/1.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/2.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/3.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/4.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/5.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/6.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/7.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/8.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/9.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/10.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/11.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/12.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/13.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/14.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/15.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/16.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/17.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/18.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/19.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/20.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/21.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/22.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/23.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/24.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/25.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/26.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/27.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/28.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/29.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851160/images/big/30.webp</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть 60%; Вискоза 35%; лайкра 5%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый; светло-серый; зернистый серый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214430,
+          20214665,
+          767344076
+        ],
+        "variable_values": [
+          "серый",
+          "светло-серый",
+          "зернистый серый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "170 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "87-68-93",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "44",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "нет",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "100%полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные; с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "двубортная",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "двубортное",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "допускается отпаривание",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто 1 шт; пояс 1 шт.",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Willines</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4070056</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>44, 46</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/10674551/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10674551</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Пальто плюс сайз с поясом демисезонное удлиненное</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8115</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Длинное демисезонное пальто делает вас стройной и модной! Выполнено из ткани содержащую чистую натуральную шерсть, цвет пальто черный, коричневый или графит, что делает его универсальным вариантом для создания разнообразных образов. Представленная модель относится к категории оверсайз, предполагает свободную посадку, подойдёт для весны и лета, без капюшона, что добавляет ему легкости и изысканности, прямой силуэт подчёркивает стройность фигуры, а длина в стиле макси создаст неповторимый образ для полных женщин, которые ценят комфорт и качество.  
+Пояс подчеркнет талию. Выполнено в классическом стиле, актуально всегда, представлено в больших размерах. 
+</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/1.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/2.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/3.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/4.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/5.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/6.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/7.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/8.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/9.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/10.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/11.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/12.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/13.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/14.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/15.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/16.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674551/images/big/17.webp</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "65% шерсть, 35% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "коричневый",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "коричневый"
+        ],
+        "variable_value_IDs": [
+          20214658
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "супатная",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "168 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "100 - 75 - 110",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "54",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "шерсть",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от +10°С до -10°С",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "удобное лекало",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "стирка при t не более 30°C; деликатный отжим",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто длинное драповое - 1шт; пояс - 1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Cassidy</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/16757</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>56, 58, 60, 62, 64, 66, 68</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/10674550/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>10674550</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Пальто оверсайз с поясом демисезонное удлиненное</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>7952</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Длинное демисезонное пальто большого размера  неповторимый стиль и элегантность, выполнено из ткани содержащую чистую натуральную шерсть, цвет пальто черный, коричневый или графит, что делает его универсальным вариантом для создания разнообразных образов. Представленная модель относится к категории оверсайз, предполагает свободную посадку, подойдёт для весны, будет тепло и уютно в непогоду, мягкая текстура ткани делает приятным на ощупь. Пальто без капюшона, что добавляет ему легкости и изысканности. Этот женский элемент гардероба отличается стильным дизайном: его прямой силуэт подчёркивает стройность фигуры, с таким пальто каждая женщина почувствует себя модной и уверенной. Оно создаст неповторимый образ для полных женщин, которые ценят комфорт и качество.  
+Особенностью этого пальто является наличие пояса, который подчеркнет вашу талию и добавит образу женственности. Выполнено в классическом стиле, актуально всегда, представлено в больших размерах. Каждая дама выберет подходящий размер и будет неотразимой 
+</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/1.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/2.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/3.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/4.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/5.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/6.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/7.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/8.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/9.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/10.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/11.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/12.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/13.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/14.webp, https://basket-01.wbbasket.ru/vol106/part10674/10674550/images/big/15.webp</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "65% шерсть, 35% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "графит",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "графит"
+        ],
+        "variable_value_IDs": [
+          20214819
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "Демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "супатная",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "168 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "100 - 75 - 110",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "50",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "шерсть",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от +10°С до -10°С",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "удобное лекало",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "Деликатная химическая чистка в щадящем режиме",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто длинное драповое - 1шт; пояс - 1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Cassidy</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/16757</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>58, 60, 62, 64, 66, 68</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/167341416/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>167341416</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Пальто классическое демисезонное</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6024</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Верхняя одежда от WORLD VOGUE в коллекции 2025 года представляет собой демисезонное женское пальто, которое гармонично сочетает в себе современные модные тенденции. Это модное изделие в осенне-весеннем стиле станет идеальным дополнением вашего гардероба.
+Модель изготовлена из качественного драпа, в состав которого входит 70% шерсти, 25% полиэстера и 5% эластана. Такой материал обеспечивает комфорт и приятные тактильные ощущения, а также позволяет носить пальто в диапазоне температур от +10 до -5 градусов. Прямой силуэт с длинными рукавами и прорезными карманами с клапаном, дополненный супатной застежкой на пуговицах, придает элегантный вид. Подкладка из вискозы добавляет дополнительный комфорт и утепление.
+Пальто доступно в различных размерах, включая большие, а также модели для беременных на ранних сроках, что делает его универсальным выбором для женщин всех возрастов и включая невысоких. Это изделие выделяется своим качеством и стильным дизайном, добавляя в ваш гардероб уникальность. Высококачественная подкладка гарантирует долговечность изделия, а модные акценты делают его трендовым и классическим одновременно.
+Это пальто идеально подходит для прогулок, офиса и вечеринок. Оно сочетает в себе классика и кэжуал, что позволяет носить его как на повседневной основе, так и в более формальной обстановке. Весна и осень - идеальные времена года для того, чтобы продемонстрировать пальто, которое отличается длинным и приталенным силуэтом, обеспечивая не только стиль, но и практичность. Утеплитель внутри гарантирует, что пальто будет согревать вас даже в более прохладные зимние дни.
+Эта одежда предназначена для создания стильного образа без лишней сложности, добавляя легкость и изящество в ваш повседневный стиль. Благодаря оверсайз фасону, оно подходит для любой фигуры и роста. Подклада из высококачественного материала обеспечивает  утепленный комфорт. 
+</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/1.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/2.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/3.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/4.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/5.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/6.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/7.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/8.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/9.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/10.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/11.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/12.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/13.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/14.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/15.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/16.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/17.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/18.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/19.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/20.webp, https://basket-12.wbbasket.ru/vol1673/part167341/167341416/images/big/21.webp</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть 70%; полиэстер 25%; Эластан 5%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "темно-синий",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214316
+        ],
+        "variable_values": [
+          "темно-синий"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы, супатная",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "174 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утепления",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "приталенный",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные, с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "стиль",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "карман",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "стирка не рекомендуется; Рекомендована химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пояс - 1 шт.",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>WORLD VOGUE</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1050876</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/452839060/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>452839060</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Пальто коричневое классическое</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Длинное пальто прекрасно защищает от ветра и визуально придаёт силуэту стройности. Такой крой универсален и подходит на все случаи жизни — будь то прогулка по парку или встреча с друзьями в кафе. С этим пальто очень легко собрать актуальный образ из Pinterest, а его стиль отлично вписывается в эстетику Old Money.
+Цветовое решение — синее женское пальто джинсового оттенка — всегда актуально и вне временных модных тенденций. Это настоящая классика жанра, которая не выходит из моды. Натуральная шерсть в составе обеспечивает комфортное тепло даже в самые прохладные дни межсезонья.
+Осенние изменения погоды больше не будут проблемой благодаря утепленному женскому верхнему слою одежды. Насыщенный черный оттенок добавляет образу лаконичности и строгой элегантности.
+Это женское демисезонное пальто отлично подойдёт как для экспериментов и новых идей аутфита для тех, кто следит за мировыми трендами, так и для ценителей практичного гардероба. Длинный крой освежает привычные образы и подчеркивает универсальный характер вещи.
+Фасон оверсайз позволяет создавать стильные многослойные наряды для холодного времени года: сочетания со свитерами или брюками становятся еще более интересными. Шерстяной материал радует своей натуральностью и долговечностью.
+Женский выбор всегда непрост — драповые варианты, шерстяные творения индустрии моды, всё это открывает простор для поиска именно «вашего» варианта, который будет дарить удовольствие и уверенность каждый день!</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/1.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/2.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/3.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/4.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/5.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/6.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/7.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/8.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/9.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/10.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/11.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/12.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/13.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/14.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/15.webp, https://basket-25.wbbasket.ru/vol4528/part452839/452839060/images/big/16.webp</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть; полиэстер; вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "коричневый; шоколадный; шоколадно-коричневый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214658,
+          20214458,
+          28017296
+        ],
+        "variable_values": [
+          "коричневый",
+          "шоколадный",
+          "шоколадно-коричневый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы; без застежки",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "173 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "87-60-89",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42-44",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -10 °C до +15 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "оверсайз",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "без элементов",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "оверсайз; Old money; классика",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "oversize",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>SANARA</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/349059</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/107713204/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>107713204</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное прямое</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7660</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женское пальто весна-очень МАЛОМЕРИТ, рекомендуем заказывать размер больше.
+Бежевое демисезонное пальто - отличный вариант для тех, кто ищет практичность, удобство и стиль. Эко-шуба с карманами подойдет для любого повседневного образа,а также впишется в любой гардероб делового стиля.  Длина пальто миди позволяет носить его как с платьем, так и с джинсами или брюками.
+Модель выполнена из высококачественного эко-меха. Теплая шерстяная ткань придаст ощущение уюта и комфорта весной или осенью. При изготовлении пальто использовались только премиум-ткани и высококачественная фурнитура. Отстрочка по всему изделию добавляет изюминки в классический стиль. 
+Женская верхняя одежда - показатель вкуса и стиля. Модное демисезонное пальто станет незаменимой вещью в гардеробе.
+Модель прямого кроя создает oversize эффект, поэтому подходит для беременных женщин. Пальто больших размеров. Застежка на кнопки, воротник стойка и карманы - удобство в каждой детали.
+Классический вариант женского полупальто придаст вашему образу стиля и лаконичности. При этом за счет воротника стойки , который застёгивается до конца, спасет от ветра и непогоды. Температурный режим от-5 до +10.
+</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/1.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/2.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/3.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/4.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/5.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/6.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/7.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/8.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/9.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/10.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/11.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/12.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/13.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/14.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/15.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/16.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/17.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/18.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/19.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/20.webp, https://basket-07.wbbasket.ru/vol1077/part107713/107713204/images/big/21.webp</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "64% шерсть, 26% акрил, 7% вискоза, 3% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "бежевый; бежевый лайт; бежевый нейтральный; ванильно-бежевый; светло-бежевый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214644,
+          20214379,
+          720993669,
+          20214463,
+          20214643
+        ],
+        "variable_values": [
+          "бежевый",
+          "бежевый лайт",
+          "бежевый нейтральный",
+          "ванильно-бежевый",
+          "светло-бежевый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "кнопки; Пришивные кнопки",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "170 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "88-63-95",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утепления",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "-5-+10",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер; вискоза; высококачественный полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "без элементов",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "Больше размеры для беременных модная модель",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка; допускается отпаривание",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "полупальто; вешалка; пакет",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5 LOVE</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/705312</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>44, 46, 48, 50, 52, 54, 42, 56</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/158589195/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>158589195</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Пальто кокон шерстяное</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3275</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Стильное пальто от  бренда Г.Гроссо Во выбор успешных женщин! Статусное полупальто благородного верблюжьего цвета кэмел. Слегка ворсистая поверхность, 50% натуральной шерсти в составе. Пальто теплое имеет классический крой кокон с английским воротником, подходит на любые размеры, но очень выгодно сидит на больших размерах плюс сайз. Пальто демисезонное на подкладке, плечо слегка спущенноле, что позводляет выбирать такое пальто даже тем, у кого полные плечи. На стройных девушках выглядит, как оверсайз. Пальто прекрасно сочетается с любым стилем в одежде, красиво смотрится с сапогами ботфортами, лоыерами, уггами. Можно дополнить образ городским рюкзаком женским или сумкой кроссбоди. Рекомендована деликатная стирка без отжима или химчистка</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/1.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/2.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/3.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/4.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/5.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/6.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/7.webp, https://basket-10.wbbasket.ru/vol1585/part158589/158589195/images/big/8.webp</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "50% шерсть; 50% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "бежевый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214644
+        ],
+        "variable_values": [
+          "бежевый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "177 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "108-88-118",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "текстиль",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Воротник",
+        "value": "отложной",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "кенгуру",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "комфорт и тепло",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>ООО ШОП ТВ</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/37763</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>48-50</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/322555095/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>322555095</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное длинное</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>4368</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Дизайнерское удлиненное демисезонное женское пальто черное – обязательная вещь в современном базовом гардеробе. Благодаря натуральной шерсти в составе в такой верхней одежде вы не замерзнете в осеннюю и весеннюю слякоть, а практичный полиэстер не даст вашему пальто промокнуть. Стильное черное пальто женское осень свободного силуэта с английским воротником сшито из материала премиум – качества с большим содержанием шерсти в составе, что пальто не скатывается и на него ничего не липнет. Женское пальто комфортное в повседневной носке, приятное на ощупь, мягкое и легкое, как кашемировое. Повседневное длинное женское пальто халат черного цвета имеет классический вид, что сделает ваш образ элегантным и презентабельным. Темные оттенки ворсистого пальто шерстяное женское всегда будут в моде, будь то в повседневных и современных образах и в стиле кэжуал (casual) эта модель будет актуальна. Классическое популярное пальто женское осенее дополнено двумя удобными прорезными карманами и мягким внутренним поясом на шлевках, который поможет создать приталенный силуэт или сделать более свободным. Подкладка внутри пальто женское длинное oversize выполнена из качественной тонкой матовой ткани, выполненной из прочного полиэстера. Элегантное пальто подростковое прямой формы с длинными рукавами со втачным плечом закрывается на застежки – пришивные кнопки. При надобности их можно слегка отрегулировать – перешить по своему размеру. Особенно актуальна такое шерстяное пальто женское весна 2025 длинное демисезонное больших размеров будет для будущих мам с округлившимся животиком. Широкая размерная линейка пальто двубортные женское начинается с 42 и заканчивается 52.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/1.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/2.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/3.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/4.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/5.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/6.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/7.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/8.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/9.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/10.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/11.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/12.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/13.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/14.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/15.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/16.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/17.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/18.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/19.webp, https://basket-19.wbbasket.ru/vol3225/part322555/322555095/images/big/20.webp</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "80% шерсть; 20% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214430
+        ],
+        "variable_values": [
+          "серый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "кнопки",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "168 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "83-61-91",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утеплителя",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от 0 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "двубортная",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто 1шт вешалка 1шт чехол 1шт пояс 1шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>MAXI STUDIO - женская верхняя одежда</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4396660</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 50</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/322552655/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>322552655</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Пальто женское весна осень</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4703</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Дизайнерское удлиненное демисезонное женское пальто черное – обязательная вещь в современном базовом гардеробе. Благодаря натуральной шерсти в составе в такой верхней одежде вы не замерзнете в осеннюю и весеннюю слякоть, а практичный полиэстер не даст вашему пальто промокнуть. Стильное черное пальто женское осень свободного силуэта с английским воротником сшито из материала премиум – качества с большим содержанием шерсти в составе, что пальто не скатывается и на него ничего не липнет. Женское пальто комфортное в повседневной носке, приятное на ощупь, мягкое и легкое, как кашемировое. Повседневное длинное женское пальто халат черного цвета имеет классический вид, что сделает ваш образ элегантным и презентабельным. Темные оттенки ворсистого пальто шерстяное женское всегда будут в моде, будь то в повседневных и современных образах и в стиле кэжуал (casual) эта модель будет актуальна. Классическое популярное пальто женское осенее дополнено двумя удобными прорезными карманами и мягким внутренним поясом на шлевках, который поможет создать приталенный силуэт или сделать более свободным. Подкладка внутри пальто женское длинное oversize выполнена из качественной тонкой матовой ткани, выполненной из прочного полиэстера. Элегантное пальто подростковое прямой формы с длинными рукавами со втачным плечом закрывается на застежки – пришивные кнопки. При надобности их можно слегка отрегулировать – перешить по своему размеру. Особенно актуальна такое шерстяное пальто женское весна 2025 длинное демисезонное больших размеров будет для будущих мам с округлившимся животиком. Широкая размерная линейка пальто двубортные женское начинается с 42 и заканчивается 52.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/1.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/2.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/3.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/4.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/5.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/6.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/7.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/8.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/9.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/10.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/11.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/12.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/13.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/14.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/15.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/16.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/17.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/18.webp, https://basket-19.wbbasket.ru/vol3225/part322552/322552655/images/big/19.webp</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "80% шерсть; 20% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "черный",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          13600062
+        ],
+        "variable_values": [
+          "черный"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "кнопки",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "168 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "83-61-91",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утеплителя",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от 0 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "двубортная",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто 1шт вешалка 1шт чехол 1шт пояс 1шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>MAXI STUDIO - женская верхняя одежда</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4396660</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/11664879/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11664879</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Пальто классическое демисезонное</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Женское демисезонное пальто Lady Jasmine — стильное прямое пальто в клетку с поясом и регулируемыми рукавами для весны и осени.
+Элегантное удлиненное пальто прямого силуэта. Классическая модель с английским воротником и уникальными рукавами — их можно регулировать по высоте, подвернув как манжеты. Пояс из основной ткани закреплен шлевками в боковых швах. 
+Качественные материалы: 70% шерсть в составе обеспечивает тепло и защиту от влаги. Драповое полотно премиум-качества с подкладкой из качественной тонкой матовой вискозы — прочной и приятной к телу. Подходит для еврозимы (-5 до +10°C).
+Российское производство, рекомендована химчистка.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/1.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/2.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/3.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/4.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/5.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/6.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/7.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/8.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/9.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/10.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/11.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/12.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/13.webp, https://basket-01.wbbasket.ru/vol116/part11664/11664879/images/big/14.webp</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть 70%; полиэстер 25%; Эластан 5%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "серый"
+        ],
+        "variable_value_IDs": [
+          20214430
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "Демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "кнопки",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "174 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утеплителя",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "- 5 до 10 градусов",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "накладные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "манжеты",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "дышащий материал",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "стирка не рекомендуется; Рекомендуется химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пояс - 1 шт.",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>LADY JASMINE</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/50684</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 46</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/325024418/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>325024418</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Пальто осеннее короткое</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4479</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стильное демисезонное короткое пальто для женщин изготовлено из высококачественной ткани в составе с натуральной шерстью. 
+Представляем вашему вниманию пальто пиджак, которое станет идеальным выбором для весны 2025. Это меховое пальто сочетает в себе элегантность и комфорт, создавая неповторимый образ. Бежевый цвет делает его универсальным и легкосочетаемым с любыми вещами из гардероба.
+Верхняя одежда для женщин обязана быть уютной и комфортной. Поэтому мы постарались предложить вам короткое пальто , которое идеально подходит для тех, кто ценит стиль и практичность. Удачный выбор для автоледи. Укороченное женское пальто весна-осень подчеркивает фигуру и отлично сочетается с различными нарядами: от повседневных для прогулок до более нарядных на свидание или мероприятие.
+С этим демисезонным коротким пальто вы будете чувствовать себя уверенно в любую погоду. Носите его как пиджак пальто — легко комбинируйте с джинсами, юбками или платьями, добавляя вашему образу нотки изысканности.
+Короткая экошубка изговтовлена из премиальных тканей с использованием высококачественной фурнитуры. 
+Бежевое короткое пальто пиджак подойдёт как к деловому стилю, и также прекрасно впишется в повседневный образ. 
+Демисезонное пальто на пуговицах  с поясом изящно подчеркнёт изгибы фигуры и скроет недостатки. 
+Размерный ряд 42-52. Вы сможете выбрать подхоящий размер.
+Не упустите возможность стать обладательницей этого стильного и функционального изделия, которое придаст вашему гардеробу свежесть и новизну. </t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/1.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/2.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/3.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/4.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/5.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/6.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/7.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/8.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/9.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/10.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/11.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/12.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/13.webp, https://basket-19.wbbasket.ru/vol3250/part325024/325024418/images/big/14.webp</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "64% шерсть, 26% акрил, 7% вискоза, 3% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "бежевый; бежевый нейтральный; ванильно-бежевый; теплый бежевый; светло-бежевый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214644,
+          720993669,
+          20214463,
+          720993799,
+          20214643
+        ],
+        "variable_values": [
+          "бежевый",
+          "бежевый нейтральный",
+          "ванильно-бежевый",
+          "теплый бежевый",
+          "светло-бежевый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "170 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "88-63-95",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "нет",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер; вискоза; акрил",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы; карманы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "с поясом",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "для среднего роста",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "допускается отпаривание; деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто; пояс; пакет",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5 LOVE</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/705312</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/235923966/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>235923966</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Пальто черное с поясом удлиненное плюс сайз</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Длинное демисезонное пальто длиной 115 см. с высокой шлицей сзади и поясом это сама элегантность, ткань содержит чистую натуральную шерсть, цвет пальто черный, что делает его универсальным вариантом для создания разнообразных образов. Представленная модель относится к категории сайз плюс, оверсайз, предполагает свободную посадку. Удлиненное пальто подойдёт для весны, будет тепло и уютно в непогоду, мягкая текстура ткани делает его приятным на ощупь. Пальто без капюшона, что добавляет ему легкости и изысканности. Этот женский элемент гардероба отличается стильным дизайном: его прямой силуэт подчёркивает стройность фигуры, а длина в стиле макси делает образ более элегантным. С таким пальто каждая женщина почувствует себя модной и уверенной. Оно создаст неповторимый образ для полных женщин, которые ценят комфорт и качество.  
+Особенностью этого пальто является наличие пояса, который подчеркнет вашу талию и добавит образу женственности. Выполнено в классическом стиле, актуально всегда, представлено в больших размерах. Каждая дама выберет подходящий размер и будет неотразимой 
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/1.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/2.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/3.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/4.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/5.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/6.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/7.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/8.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/9.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/10.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/11.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/12.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/13.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/14.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/15.webp, https://basket-15.wbbasket.ru/vol2359/part235923/235923966/images/big/16.webp</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "70% шерсть, 30% акрил",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "черный",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "черный"
+        ],
+        "variable_value_IDs": [
+          13600062
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "Демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "супатная",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "168 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "100 - 75 - 110",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "52",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "шерсть",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от +10°С до -10°С",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "со шлицей",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "Деликатная химическая чистка в щадящем режиме",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто длинное драповое - 1шт; пояс - 1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Cassidy</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/16757</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>54, 56, 58, 60, 62, 64, 66, 68, 52</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/467538239/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>467538239</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Пальто коричневое весна-осень длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>9900</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Наступили теплые и прохладные дни, и значит настало время обновить гардероб! Пальто женское весна-осень станет универсальным спутником для городской жизни. Оно подчеркнёт ваш неповторимый стиль, благодаря элегантному фасону и лёгкости комбинирования с любой одеждой.
+Это пальто осеннее женское создано для тех, кто ценит комфорт и не боится экспериментировать с образом. Пальто весеннее женское, выполненное в стиле оверсайз с объемным плечем, дарит простор движениям и создает ощущение уюта. Мягкая ткань согревает в свежем утреннем воздухе, делая каждое перемещение на улицу настоящим удовольствием.
+Пальто длинное прекрасно защищает от ветра, придаёт силуэту стройности. Такой крой подходит на все случаи жизни — будь то прогулка по парку или встреча с друзьями в кафе. Под данное пальто очень легко собрать актуальный образ из Pinterest. Также оно подходит под стиль Old Money.
+Касательно цвета — синее пальто женское джинсового всегда актуально и вне модных тенденций! Это классика жанра, которая никогда не выходит из моды. Натуральная шерсть обеспечивает тепло даже в самые прохладные дни межсезонья.
+Осенние изменения погоды перестанут быть проблемой благодаря утепленному женскому верхнему слою одежды! Насыщенный черный оттенок добавляет лаконичности и строгости вашему стилю.
+Это женское демисезонное пальто подходит как для новых идей аутфита тех, кто следит за мировыми трендами, так и для любителей практичного гардероба. Длинное решение серьезно освежает образы многих женщин благодаря своему универсальному характеру.
+Оверсайз позволяет создать потрясающие многослойные наряды для холодного времени года и сочетания со свитерами или брюками становятся еще интереснее! Шерстяной материал радует своей натуральностью и долговечностью.
+Женский выбор всегда остается сложной задачей – сколько бы мы ни говорили о драповых вариантах или шерстяных творениях индустрии моды; выбор "вашего" варианта будет сопровождаться моментом счастья каждый день использования!</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/1.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/2.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/3.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/4.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/5.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/6.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/7.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/8.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/9.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/10.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/11.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/12.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/13.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/14.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/15.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/16.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/17.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/18.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/19.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/20.webp, https://basket-26.wbbasket.ru/vol4675/part467538/467538239/images/big/21.webp</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть - 80%, полиэстер - 18%, кашемир - 2%, Подкладка - 100% полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "коричневый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214658
+        ],
+        "variable_values": [
+          "коричневый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "165 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "85-60-90",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "оверсайз",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "однобортная; со шлицей",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто + пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Giulia Rosetti</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/39919</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>54 на рост - 165-172, 60 на рост - 165-172, 42 на рост - 173-180, 44 на рост - 173-180, 48 на рост - 173-180, 56 на рост - 173-180, 58 на рост - 173-180, 60 на рост - 173-180</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/260422605/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>260422605</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное оверсайз</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>4577</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Если ищете базовый, но в то же время стильный способ сказать весне и осени «привет», это женская верхняя одежда для вас. Дизайнерская коллекция вдохновлена трендами Pinterest, чтобы даже школьная форма выглядела как будто вы только что вернулись с модного показа. Классическая модель с воротником, поясом и рукавом сразу намекает: тут мода не просто приходит — она правит бал! Для девушек, женщин, подростков и девочек — каждый найдет свой образ. Трендовая длина подходит невысоким барышням и тем, кто любит короткое пальто. Подчеркнутая талия делает его отличным вариантом для беременных или просто поклонниц деловой офисной одежды.
+Этот стильный и удобный вариант из Киргизии разработан специально для тех, кто ценит комфорт и элегантность в одном флаконе. Теплая ткань сохраняет уют даже при переменчивой погоде, а универсальный дизайн легко впишется в повседневный образ. В 2025 году такой выбор станет настоящей находкой для модниц, которые предпочитают брендовые вещи с характером и душой. Размеров много, так что подобрать подходящий вариант не составит труда.
+Модная деталь — драповое полотно с натуральным составом: тепло встречает даже капризную погоду. Весенняя свежесть и осенняя строгость сочетаются в каждой строчке этой вещи. Неважно, идете ли вы в школу или на работу, пальто легко впишется в любой офис или даже школу для подростка.
+</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/1.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/2.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/3.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/4.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/5.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/6.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/7.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/8.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/9.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/10.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/11.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/12.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/13.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/14.webp, https://basket-16.wbbasket.ru/vol2604/part260422/260422605/images/big/15.webp</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "полиамид; полиэстeр; шерсть",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "серый"
+        ],
+        "variable_value_IDs": [
+          20214430
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "Круглогодичный",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "175 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "89-66-96",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утеплителя",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +15 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "свободный",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "двубортная",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "сухая химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто - 1; Пояс - 1; Вешалка - 1; чехол - 1",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>KUMAYIBA</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/757552</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/265940261/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>265940261</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Пальто серое весна-осень длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9275</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Наступили теплые и прохладные дни, и значит настало время обновить гардероб! Пальто женское весна-осень станет универсальным спутником для городской жизни. Оно подчеркнёт ваш неповторимый стиль, благодаря элегантному фасону и лёгкости комбинирования с любой одеждой.
+Это пальто осеннее женское создано для тех, кто ценит комфорт и не боится экспериментировать с образом. Пальто весеннее женское, выполненное в стиле оверсайз с объемным плечем, дарит простор движениям и создает ощущение уюта. Мягкая ткань согревает в свежем утреннем воздухе, делая каждое перемещение на улицу настоящим удовольствием.
+Пальто длинное прекрасно защищает от ветра, придаёт силуэту стройности. Такой крой подходит на все случаи жизни — будь то прогулка по парку или встреча с друзьями в кафе. Под данное пальто очень легко собрать актуальный образ из Pinterest. Также оно подходит под стиль Old Money.
+Касательно цвета — синее пальто женское джинсового всегда актуально и вне модных тенденций! Это классика жанра, которая никогда не выходит из моды. Натуральная шерсть обеспечивает тепло даже в самые прохладные дни межсезонья.
+Осенние изменения погоды перестанут быть проблемой благодаря утепленному женскому верхнему слою одежды! Насыщенный черный оттенок добавляет лаконичности и строгости вашему стилю.
+Это женское демисезонное пальто подходит как для новых идей аутфита тех, кто следит за мировыми трендами, так и для любителей практичного гардероба. Длинное решение серьезно освежает образы многих женщин благодаря своему универсальному характеру.
+Оверсайз позволяет создать потрясающие многослойные наряды для холодного времени года и сочетания со свитерами или брюками становятся еще интереснее! Шерстяной материал радует своей натуральностью и долговечностью.
+Женский выбор всегда остается сложной задачей – сколько бы мы ни говорили о драповых вариантах или шерстяных творениях индустрии моды; выбор "вашего" варианта будет сопровождаться моментом счастья каждый день использования!</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbbasket.ru/vol2659/part265940/265940261/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть - 80%, полиэстер - 20%. Подкладка - 100% полиэстер.",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый меланж; серый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214508,
+          20214430
+        ],
+        "variable_values": [
+          "серый меланж",
+          "серый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "165 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "85-60-90",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5°C до +15°С",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "оверсайз",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "однобортная; со шлицей",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто + пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Giulia Rosetti</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/39919</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>42 на рост - 165-172, 44 на рост - 165-172, 48 на рост - 165-172, 54 на рост - 165-172, 56 на рост - 165-172, 58 на рост - 165-172, 60 на рост - 165-172, 64 на рост - 165-172, 54 на рост - 173-180, 56 на рост - 173-180</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/306851990/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>306851990</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное прямое с поясом</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5194</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Длинное шерстяное двубортное женское пальто  макси прямого кроя из плотной драповой ткани из натуральной шерсти идеально подойдет для еврозимы.
+Широкий отложной воротник с лацканами. Длинные свободные рукава с прямыми манжетами. Два прорезных кармана без застежки по бокам. Застежка на крупные пуговицы спереди, пояс в комплекте. Прямой нижний край с длинной шлицей (разрезом) сзади
+Классическое однотонное плотное шоколадное пальто из новой весенней коллекции. Теплое демисезонное пальто классического кроя с натуральной шерстью в составе защитит от холодных весенних и осенних ветров и других капризов погоды. Стильное и универсальное: создавай самые теплые и женственные аутфиты на каждый день.
+Пальто будет прекрасно выглядить как в классических строгих образах, так и стильно будет смотреться в кэжуал повседневных образах.Для беременных девушек - это действительно комфортное решение, а его приталенная форма с поясом подчеркнет вашу фигуру, придавая изящство. Также это оверсайз пальто впишется в молодежный стиль и идеально подойдет на работу, в школу или университет.Если вы ищете теплую верхнюю одежду для женщин, это пальто может стать вашим идеальным выбором.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/1.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/2.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/3.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/4.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/5.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/6.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/7.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/8.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/9.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/10.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/11.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/12.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/13.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/14.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/15.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/16.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/17.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/18.webp, https://basket-19.wbbasket.ru/vol3068/part306851/306851990/images/big/19.webp</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть 60%; Вискоза 35%; лайкра 5%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "коричневый; шоколадный; шоколадно-коричневый",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "коричневый",
+          "шоколадный",
+          "шоколадно-коричневый"
+        ],
+        "variable_value_IDs": [
+          20214658,
+          20214458,
+          28017296
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "170 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "87-68-93",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "44",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "нет",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "100%полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные; с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "двубортная",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто 1 шт; пояс 1 шт.",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Willines</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4070056</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/277883751/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>277883751</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Полупальто шерстяное</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>8153</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Серое полупальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Полупальто в деловом стиле — удачное решение для офисного гардероба. Это сдержанная элегантность, уверенность и профессионализм. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbbasket.ru/vol2778/part277883/277883751/images/big/1.webp, https://basket-17.wbbasket.ru/vol2778/part277883/277883751/images/big/2.webp, https://basket-17.wbbasket.ru/vol2778/part277883/277883751/images/big/3.webp, https://basket-17.wbbasket.ru/vol2778/part277883/277883751/images/big/4.webp, https://basket-17.wbbasket.ru/vol2778/part277883/277883751/images/big/5.webp</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть натуральная 100%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214430
+        ],
+        "variable_values": [
+          "серый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "175 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5 °C до +10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Воротник",
+        "value": "отложной",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "Без капюшона, теплый",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "Химическая стирка; стирка запрещена; отбеливание запрещено",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>44, 52</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/39188958/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>39188958</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Пальто зимнее длинное</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7633</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>ЗИМА арт 39188958. Идеальное двубортное женское пальто. Элегантный прямой силуэт с поясом, накладные карманы, в сочетании с классическим английским воротником создают утонченный силуэт. Выполнено из натуральных премиум тканей с высоким содержанием шерсти, при этом мягких и легких будут приятны и долговечны в носке. С такой вещью удобно строить базовый гардероб.Соответствует таблице размеров. Прекрасно подойдет в качестве подарка для сестры, мамы, бабушки. Данная модель пользуется популярностью у молодых мам. А если Вы поклонник стиля oversize, просто закажите вещь на размер больше.  Идеально в качестве одежды для женщин больших размеров.
+Параметры модели:Рост - 162 см;Обхват груди - 85 см;Обхват талии - 60 см;Обхват бедер - 90 см.Размер на модели: 42.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/1.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/2.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/3.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/4.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/5.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/6.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/7.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/8.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/9.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/10.webp, https://basket-03.wbbasket.ru/vol391/part39188/39188958/images/big/11.webp</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "80% шерсть, 20 % полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "глубокий черный; черный",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214385,
+          13600062
+        ],
+        "variable_values": [
+          "глубокий черный",
+          "черный"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "зима",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "164 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "85-62-91",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "Зимнее пальто с утеплителем слимтекс",
+        "charc_type": 1
+      },
+      {
+        "name": "Плотность синтетического утеплителя",
+        "value": "200 г/кв.м",
+        "charc_type": 4
+      },
+      {
+        "name": "Температурный режим",
+        "value": "+10-20",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "поливискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "накладные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "с подкладкой",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "шлевки",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка; химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто женское зимнее -1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Jadelier</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4082760</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 40, 52, 54, 58</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/131686600/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>131686600</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное драповое</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>4381</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Ищете стильное  женское пальто драповое на осень весну? Представляем вам нашу трендовую модель пальто оверсайз женское драп прямого кроя весна 2024 в стиле oversize - идеальный выбор повседневной верхней одежды для модных и практичных женщин! Двубортное теплое шерстяное изделие на пуговицах с поясом выполнено из высококачественных материалов, хорошо держит форму и выгодно подчеркивает все достоинства фигуры. Натуральная шерсть в составе, с добавлением вискозы, дарит тепло и комфорт в холодное осеннее и демисезонное время года. Теплое по фактуре, в сочетании с подкладкой из плотного полиэстера - отличный вариант на прохладный сезон. Оригинальный дизайн, подклад под пальто, классическое и элегантное исполнение идеально сочетается с разнообразными предметами гардероба, ведь черное – это классика и подходит ко всему. Носить пальто черное оверсайз можно в разных вариациях: прямой покрой для строгого, делового образа, а так же с поясом. Модное, удлиненное хорошо смотрится в любой ситуации. Благодаря свободному крою оверсайз не сковывает движения в течение всего дня, поэтому подойдет для беременных и будущих мам. Длинные рукава со спущенной линией плеча и прорезные боковые карманы добавляют удобства и универсальности. Длина миди визуально стройнит и в зависимости от роста садится до или ниже колена, что актуально как для высоких, так и для невысоких девушек. Молодежный, современный фасон позволит создавать многослойные, утепленные луки. Английский воротник придает особый шарм и защищает от ветра. Базовое сочетание стиля и комфорта.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/1.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/2.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/3.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/4.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/5.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/6.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/7.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/8.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/9.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/10.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/11.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/12.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/13.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/14.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/15.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/16.webp, https://basket-10.wbbasket.ru/vol1316/part131686/131686600/images/big/17.webp</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть; 40%; вискоза; 30%; полиэстер; 30%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "черный",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          13600062
+        ],
+        "variable_values": [
+          "черный"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы; пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "167 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "85-64-94",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "М",
+        "charc_type": 1
+      },
+      {
+        "name": "Длина изделия по спинке",
+        "value": "107 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Утеплитель",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -10 до +10",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "оверсайз",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "Английский воротник",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "ветрозащита",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "допускается отпаривание; химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто женское - 1 штука; Пояс - 1 штука",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>LiLu Mag</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/166137</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/384408832/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>384408832</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Пальто халат с поясом демисезонное</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>5067</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Фиолетовое пальто женское французского бренда Maison David. Состав: 60% вискоза, 40% шерсть натуральная. Вискоза делает материал струящимся, шелковистым и приятным на ощупь, а шерсть — теплым и комфортным. Состав согревает и позволяет коже дышать, в нем не жарко и не холодно.
+Верхняя одежда имеет прямой силуэт. Модель отличает шалевый воротник и наличие накладных карманов.
+Пальто в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-22.wbbasket.ru/vol3844/part384408/384408832/images/big/1.webp, https://basket-22.wbbasket.ru/vol3844/part384408/384408832/images/big/2.webp, https://basket-22.wbbasket.ru/vol3844/part384408/384408832/images/big/3.webp, https://basket-22.wbbasket.ru/vol3844/part384408/384408832/images/big/4.webp, https://basket-22.wbbasket.ru/vol3844/part384408/384408832/images/big/5.webp, https://basket-22.wbbasket.ru/vol3844/part384408/384408832/images/big/6.webp</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "вискоза 60%; шерсть натуральная 40%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серо-фиолетовый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214863
+        ],
+        "variable_values": [
+          "серо-фиолетовый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "175 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "накладные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "Без капюшона, теплый",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>48, 50</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/197590259/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>197590259</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Пальто с шерстью однобортное</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>5003</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Стильное пальто меланжево-серого оттенка. Выполнено из плотного материала с мягкой ворсистой текстурой. Натуральная овечья шерсть отвечает за поддержание оптимальной температуры, а прочные поливолокна не позволяют изделию деформироваться со временем. Модель прямого силуэта, с длинным втачным рукавом, отложным воротником с заостренным лацканом, однобортной застёжкой на две пуговицы и карманами с клапанами. Базовое пальто дополнит как деловой образ, так и лук в стиле кэжуал.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/1.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/2.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/3.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/4.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/5.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/6.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/7.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/8.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/9.webp, https://basket-13.wbbasket.ru/vol1975/part197590/197590259/images/big/10.webp</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "Овечья шерсть - 55%, Полиэстер - 35%, Вискоза - 10%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214430
+        ],
+        "variable_values": [
+          "серый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "177 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "83-61-89",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "44",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от +10 °C до -1 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "поливискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "с клапаном",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "casual",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ELIS</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/53029</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/99827351/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>99827351</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Пальто классическое демисезонное</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>5163</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Современное демисезонное пальто World Vogue без утеплителя прямого, зауженного к низу силуэта. Длина пальто фиксированная для всех размеров - 116 см. (±3%). Длина рукава в размерах 42 по 46 - 63 см., в размерах от 48 и далее - 64 см. Рекомендованный температурный режим от +10 до -5 градусов. Втачной рукав делает посадку более классической и вытягивает силуэт. Пальто застегивается на кнопку, с внутренней стороны в правом боковом шве вшит хлястик для крепления полы пальто. Пояс из основной ткани в комплекте, имеются шлевки для пояса. Для удобства ходьбы предусмотрены разрезы по бокам. На фото представлено два варианта: классический и ежедневный. Рост девушки модели 174 см. Разрешена химчистка. Мы не рекомендуем стирку, т.к. возможна усадка и деформация. Мы, производитель пальто, не осуществляем продажи напрямую со своего склада. Все наши изделия хранятся на складах Wildberries и отправляются к Вам со складов WB, исходя из Ваших заявок. Мы не задерживаем отправку наших превосходных пальто, так как фактически не участвуем в этом процессе. При отправке наших изделий мы не путаем их с товаром других марок, так как производим исключительно свои классические модели. Мы не производим пересортировку по моделям, размерам, или расцветкам, потому что не участвуем в формировании отправок на объектах WB. Мы не переупаковываем наши изделия в "непонятно что" на складах данного интернет-магазина, в связи с тем, что не имеем доступа к этим объектам. Мы не удерживаем с Вас стоимость возвратов, также как не выдаём чеки о покупке, поскольку продажей занимается другая для нас организация - WB. Мы подвергаем наши изделия контролю перед отправкой в Wildberries, не допуская путаницы или повреждений. Мы гарантируем, что наши пальто отправляются в WB полностью укомплектованными, обязательно с поясами, подготовленными и отпаренными, упакованными в запаянные полиэтиленовые чехлы, с индивидуальной вешалкой.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/1.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/2.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/3.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/4.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/5.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/6.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/7.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/8.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/9.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/10.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/11.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/12.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/13.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/14.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/15.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/16.webp, https://basket-05.wbbasket.ru/vol998/part99827/99827351/images/big/17.webp</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть 70 %; полиэстер 25 %; эластан 5 %",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "черный",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          13600062
+        ],
+        "variable_values": [
+          "черный"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "кнопки",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "174 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утепления",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "- 5 до 10 градусов",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "классическое пальто",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "классическое",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "шлевки",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "стирка запрещена; химическая чистка разрешена",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто - 1 шт., пояс - 1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>WORLD VOGUE</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1050876</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/336626766/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>336626766</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное серое Весна/Осень с поясом</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>5163</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Женское длинное серое шерстяное пальто — идеальное демисезонное
+Ищете элегантную верхнюю одежду на весну и осень? Это классическое женское пальто из натуральной шерсти свободного кроя станет базой гардероба. Наше шерстяное длинное пальто в благородном сером цвете — стильное демисезонное решение. Пальто с поясом позволяет менять силуэт, создавая как строгий офисный, так и непринужденный повседневный образ.
+Ключевые особенности и преимущества:
+· Универсальная длина 130 см: Длинное пальто элегантно скрывает бедра и подходит для любого роста.
+· Два силуэта в одном: Пояс в комплекте подчеркивает талию, создавая элегантный или расслабленный вид.
+· Практичные детали: Английский воротник, цельнокроеные рукава с отворотами для регулировки длины, удобные прорезные карманы.
+· Качество и комфорт: Состав — 60% шерсть, 30% полиэстер, 10% вискоза. Теплая ткань держит форму. Подкладка в тон и шлица обеспечивают удобство.
+С чем носить это женское демисезонное пальто?
+· Деловой стиль: Сочетайте с брюками, рубашкой и лоферами.
+· Повседневный образ: Наденьте с джинсами, объемным свитером и кроссовками.
+· Вечерний выход: Комбинируйте с платьем-миди и сапогами на каблуке.
+Это пальто 2026 года — тренд, который будет актуальен долгие сезоны. Выбирайте российское пальто с размерной сеткой 42, 44, 46, 48, 50 для идеальной посадки. Демисезонное женское пальто свободного кроя — выгодное вложение в ваш стиль. Верхняя одежда должна быть безупречной!</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/1.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/2.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/3.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/4.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/5.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/6.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/7.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/8.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/9.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/10.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/11.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/12.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/13.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/14.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/15.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/16.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/17.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/18.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/19.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/20.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/21.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/22.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/23.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/24.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/25.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/26.webp, https://basket-20.wbbasket.ru/vol3366/part336626/336626766/images/big/27.webp</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "60% шерсть, 30% полиэстер, 10% вискоза",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый графит",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214627
+        ],
+        "variable_values": [
+          "серый графит"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "173 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "89-66-93",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "44",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от +10°С до -10°С",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "свободный",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "прорезные",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Macle A More</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/571062</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/389672001/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>389672001</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень длинное</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>4810</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Если ищете базовый, но в то же время стильный способ сказать весне и осени «привет», это женская верхняя одежда для вас. Дизайнерская коллекция вдохновлена трендами Pinterest, чтобы даже школьная форма выглядела как будто вы только что вернулись с модного показа. Классическая модель с воротником, поясом и рукавом сразу намекает: тут мода не просто приходит — она правит бал! Для девушек, женщин, подростков и девочек — каждый найдет свой образ. Трендовая длина подходит невысоким барышням и тем, кто любит длинное пальто. Подчеркнутая талия делает его отличным вариантом для беременных или просто поклонниц деловой офисной одежды.
+Этот стильный и удобный вариант из Киргизии разработан специально для тех, кто ценит комфорт и элегантность в одном флаконе. Теплая ткань сохраняет уют даже при переменчивой погоде, а универсальный дизайн легко впишется в повседневный образ. В 2025 году такой выбор станет настоящей находкой для модниц, которые предпочитают брендовые вещи с характером и душой. Размеров много, так что подобрать подходящий вариант не составит труда.
+Модная деталь — драповое полотно с натуральным составом: тепло встречает даже капризную погоду. Весенняя свежесть и осенняя строгость сочетаются в каждой строчке этой вещи. Неважно, идете ли вы в школу или на работу, пальто легко впишется в любой офис или даже школу для подростка.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/1.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/2.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/3.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/4.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/5.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/6.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/7.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/8.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/9.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/10.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/11.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/12.webp, https://basket-22.wbbasket.ru/vol3896/part389672/389672001/images/big/13.webp</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "шерсть - 30%; вискоза - 40%; полиэстер - 30%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "серый",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214430
+        ],
+        "variable_values": [
+          "серый"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы; пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "165 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "85-60-85",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "без утеплителя; без утепления",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от -5°C до +15°С",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "полиэстер",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "прямой",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "накладные",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без капюшона",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без опушки",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "без элементов; пуговицы; пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "ветрозащита; износостойкость",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка; бережная стирка при 30 градусах; сухая химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "пальто; пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Serov GROUP</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1373064</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>44, 40, 50</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/265598983/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>265598983</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное оверсайз</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>4599</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Позвольте представить вам нашу новинку – пальто на пуговицах – истинное воплощение элегантности и стиля кэжуал. Это классическое женское пальто воплощает все тенденции моды 2024 года. Длинное и женственное, оно сделает вас по-настоящему особенной. Это утепленное пальто - халат идеально подходит для осенних прогулок, весенних вечеров и даже для теплых зимних дней.  пальто оверсайз добавит шик и изысканность, придавая вашему образу особый шарм, а вместительные глубокие карманы станут удобным дополнением к любому образу. Наслаждайтесь комфортом нашего пальто, состоящего из натуральной шерсти высокого качества, благодаря чему оно не мнется и является износостойким. Его утепление обеспечит вам защиту от холода. Благодаря своему дизайну на запах и наличию пояса, наше зимнее пальто поможет вам подчеркнуть свою талию и создать идеальную силуэт. Пальто предаставлено широким размерным рядом, включая стандартные и большие размеры плюс сайз, поэтому оно отлично подойдет для всех типов фигур, в том числе и для полных, подчеркивая только достоинства фигуры. Также станет незаменимым элементом гардероба для беременных, не сковывая движения благодаря свободному крою oversize. Изысканное черное пальто позволит вам выразить свой стиль и подчеркнуть безупречный вкус классика. Женское зимнее пальто станет замечательным решением для создания нежного и романтичного образа на весну. Демисезонное шерстяное пальто является универсальным и будет сочетаться со всеми элементами гардероба: Специально подобранный цветовой ряд подчеркнет вашу индивидуальность. Независимо от того, предпочитаете ли вы стиль оверсайз или более прилегающий крой, наше пальто идеально подойдет вам. Мы создали драповое пальто и стремились воплотить требования наших самых требовательных покупателей – девочек, молодых девушек, школьниц и взрослых женщин. Позвольте себе быть модной и стильной в этом пальто макси.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/1.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/2.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/3.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/4.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/5.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/6.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/7.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/8.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/9.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/10.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/11.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/12.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/13.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/14.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/15.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/16.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/17.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/18.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/19.webp, https://basket-17.wbbasket.ru/vol2655/part265598/265598983/images/big/20.webp</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "полиамид 15%; полиэстер 25%; шерсть 60%",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "айвори",
+        "charc_type": 1,
+        "is_variable": true,
+        "variable_values": [
+          "айвори"
+        ],
+        "variable_value_IDs": [
+          25477709
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "Демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "пуговицы; пальто длинное на пуговицах",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "173 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "88 - 63 - 90",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "Без утеплителя демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Плотность синтетического утеплителя",
+        "value": "2 г/кв.м",
+        "charc_type": 4
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от 5 °C до +15 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "Полиэстер - подкладка",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "удлиненный",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "Листочка; врезной",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "длинные",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции капюшона",
+        "value": "без",
+        "charc_type": 1
+      },
+      {
+        "name": "Опции опушки",
+        "value": "без",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "с пояс карманами",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "пальто весеннее удлиненное",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "сухая химчистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "Пальто оверсайз 1 шт; пояс 1 шт",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>KUMAIBA</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/181189</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/187831451/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>187831451</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное оверсайз</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>4824</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Пальто женское от "FANCY CODE" — это ваш идеальный выбор для создания стильного образа в любое время года! Наши весенние модели — легкие и яркие, идеально подходят для прохладных дней, а осенние пальто, выполненные из высококачественной шерсти и драпа, подарят вам уют и тепло в холодную погоду.
+Демисезонное пальто — незаменимый элемент гардероба, который легко адаптируется к переменчивым условиям весны и осени. Стильный дизайн и практичность наших моделей делают их идеальными для любого сезона. Теплое утепленное изделие с натуральным утеплителем обеспечит комфорт даже в самые морозные зимние дни.
+Двубортное пальто с поясом и пуговицами не только подчеркнет вашу элегантность, но и создаст максимальный комфорт. Модели оверсайз и плюс сайз идеально подойдут для полных женщин и беременных, обеспечивая свободу движений и стильный вид. Для молодежи мы предлагаем актуальные и модные модели, которые подчеркнут индивидуальность и соответствие последним трендам.
+Пальто с английским воротником, качественной подкладкой и шерстяным утеплителем станет настоящим акцентом вашего образа, подчеркивая ваш хороший вкус. Драповое пальто — это классика, проверенная временем, с высоким качеством и долговечностью. Мы также предлагаем модели на запах, которые идеально подходят для зимы, сочетая легкость и уют.
+Не упустите возможность обыграть ваше драповое пальто различными аксессуарами, добавляя шарм и изюминку в ваш стиль. "FANCY CODE" — прямой производитель, который тщательно контролирует качество на каждом этапе производства и использует только лучшие материалы. Обновите свой гардероб с нашими пальто и наслаждайтесь комфортом и стилем в любое время года!</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/1.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/2.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/3.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/4.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/5.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/6.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/7.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/8.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/9.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/10.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/11.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/12.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/13.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/14.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/15.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/16.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/17.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/18.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/19.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/20.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/21.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/22.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/23.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/24.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/25.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/26.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/27.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/28.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/29.webp, https://basket-12.wbbasket.ru/vol1878/part187831/187831451/images/big/30.webp</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "group_name": "Основная информация",
+    "options": [
+      {
+        "name": "Состав",
+        "value": "50% шерсть 33% акрил 17% спандекс",
+        "charc_type": 1
+      },
+      {
+        "name": "Цвет",
+        "value": "какао; бежевый; коричневый; светло-коричневый; кофейный",
+        "is_variable": true,
+        "charc_type": 1,
+        "variable_value_IDs": [
+          20214495,
+          20214644,
+          20214658,
+          20214505,
+          20214329
+        ],
+        "variable_values": [
+          "какао",
+          "бежевый",
+          "коричневый",
+          "светло-коричневый",
+          "кофейный"
+        ]
+      },
+      {
+        "name": "Пол",
+        "value": "Женский",
+        "charc_type": 1
+      }
+    ]
+  },
+  {
+    "group_name": "Дополнительная информация",
+    "options": [
+      {
+        "name": "Сезон",
+        "value": "демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Вид застежки",
+        "value": "Пуговицы и петли",
+        "charc_type": 1
+      },
+      {
+        "name": "Рост модели на фото",
+        "value": "169 см",
+        "charc_type": 4
+      },
+      {
+        "name": "Параметры модели на фото (ОГ-ОТ-ОБ)",
+        "value": "78-60-88",
+        "charc_type": 1
+      },
+      {
+        "name": "Размер на модели",
+        "value": "42/164",
+        "charc_type": 1
+      },
+      {
+        "name": "Утеплитель",
+        "value": "Без утеплителя демисезон",
+        "charc_type": 1
+      },
+      {
+        "name": "Температурный режим",
+        "value": "от +10 °C до -10 °C",
+        "charc_type": 1
+      },
+      {
+        "name": "Материал подкладки",
+        "value": "Вискоза 55% Полиэстер 45%",
+        "charc_type": 1
+      },
+      {
+        "name": "Покрой",
+        "value": "Прямой покрой свободный",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип карманов",
+        "value": "Прорезанные боковые карманы",
+        "charc_type": 1
+      },
+      {
+        "name": "Тип рукава",
+        "value": "цельнокройный длинный рукав",
+        "charc_type": 1
+      },
+      {
+        "name": "Декоративные элементы",
+        "value": "Пуговицы в тон ткани",
+        "charc_type": 1
+      },
+      {
+        "name": "Особенности модели",
+        "value": "Большие размеры / для беременных / будущие мамы",
+        "charc_type": 1
+      },
+      {
+        "name": "Конструктивные элементы",
+        "value": "карман",
+        "charc_type": 1
+      },
+      {
+        "name": "Уход за вещами",
+        "value": "деликатная химическая чистка",
+        "charc_type": 1
+      },
+      {
+        "name": "Комплектация",
+        "value": "демисезонное пальто; пальто женское демисезонное; пакет; пояс",
+        "charc_type": 1
+      },
+      {
+        "name": "Страна производства",
+        "value": "Россия",
+        "charc_type": 1
+      }
+    ]
+  }
+]</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>МАГАЗИН</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/705325</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 46, 48, 50, 52</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>851</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
